--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_8_15.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_8_15.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>232163.6286437827</v>
+        <v>238372.1657568595</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9419702.262430297</v>
+        <v>9167573.323130395</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21951588.97520502</v>
+        <v>22176453.17582963</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3988837.604406056</v>
+        <v>3917240.709608862</v>
       </c>
     </row>
     <row r="11">
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2128,13 +2128,13 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2150,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -2368,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2435,19 +2435,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2548,16 +2548,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2669,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2757,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2788,13 +2788,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -2952,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3000,13 +3000,13 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3019,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3183,16 +3183,16 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3310,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -3426,13 +3426,13 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3502,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3617,16 +3617,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -3654,16 +3654,16 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3787,10 +3787,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3857,19 +3857,19 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>13.21199999999999</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3936,16 +3936,16 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>13.212</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>30.62859109457542</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>16.15985641720184</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>31.00985641720184</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>30.62859109457542</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>45.47859109457542</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>16.15985641720184</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>30.68126532262642</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>30.68126532262642</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>45.75</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>15.77859109457542</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>14.54545454545454</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>15.77859109457542</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>30.62859109457542</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>44.84848484848484</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>29.69696969696969</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>16.05</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>46.65454545454546</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>31.5030303030303</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>16.35151515151515</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>218.0443636077946</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>233.2288069297862</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>227.5226553378255</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>226.5437972649326</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>227.3888445875159</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>228.9206138457218</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>126.0247587421384</v>
+        <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>136.452118219642</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>136.686266572327</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>139.9540339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>129.1040139701257</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>140.5491878406708</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>132.3314640181038</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>138.8835099350781</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>133.8122828386153</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>137.7950954230149</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>126.5817411865447</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>137.4369974682362</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>91.99244221512848</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K11" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L11" t="n">
-        <v>70.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M11" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N11" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O11" t="n">
-        <v>53.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P11" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q11" t="n">
-        <v>108.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K12" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L12" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P12" t="n">
-        <v>26.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q12" t="n">
-        <v>68.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L13" t="n">
-        <v>64.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M13" t="n">
-        <v>65.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N13" t="n">
-        <v>55.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O13" t="n">
-        <v>71.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P13" t="n">
-        <v>80.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>91.99244221512848</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K14" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L14" t="n">
-        <v>70.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M14" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N14" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O14" t="n">
-        <v>53.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P14" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q14" t="n">
-        <v>108.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K15" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L15" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P15" t="n">
-        <v>26.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q15" t="n">
-        <v>68.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L16" t="n">
-        <v>64.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M16" t="n">
-        <v>65.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N16" t="n">
-        <v>55.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O16" t="n">
-        <v>71.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P16" t="n">
-        <v>80.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>91.99244221512848</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K17" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L17" t="n">
-        <v>70.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M17" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N17" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O17" t="n">
-        <v>53.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P17" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q17" t="n">
-        <v>108.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K18" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L18" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P18" t="n">
-        <v>26.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q18" t="n">
-        <v>68.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L19" t="n">
-        <v>64.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M19" t="n">
-        <v>65.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N19" t="n">
-        <v>55.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O19" t="n">
-        <v>71.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P19" t="n">
-        <v>80.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>106.3863816090679</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K20" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L20" t="n">
-        <v>70.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M20" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N20" t="n">
-        <v>57.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O20" t="n">
-        <v>53.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P20" t="n">
-        <v>95.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q20" t="n">
-        <v>123.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K21" t="n">
-        <v>62.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L21" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M21" t="n">
-        <v>14.61488351249857</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P21" t="n">
-        <v>41.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q21" t="n">
-        <v>68.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>88.72555822021249</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L22" t="n">
-        <v>79.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M22" t="n">
-        <v>80.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N22" t="n">
-        <v>55.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O22" t="n">
-        <v>86.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P22" t="n">
-        <v>80.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>91.99244221512848</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K23" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L23" t="n">
-        <v>84.58142974081105</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M23" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N23" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O23" t="n">
-        <v>68.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P23" t="n">
-        <v>95.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q23" t="n">
-        <v>123.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>88.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K24" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L24" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3319101965408322</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>23.30877436417577</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P24" t="n">
-        <v>26.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q24" t="n">
-        <v>83.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L25" t="n">
-        <v>64.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M25" t="n">
-        <v>80.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N25" t="n">
-        <v>70.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O25" t="n">
-        <v>86.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P25" t="n">
-        <v>95.19827131193951</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>106.9924422151285</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K26" t="n">
-        <v>101.6217957685986</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L26" t="n">
-        <v>85.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M26" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N26" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O26" t="n">
-        <v>67.70596488597789</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P26" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q26" t="n">
-        <v>108.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>88.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K27" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L27" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M27" t="n">
-        <v>14.61488351249858</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P27" t="n">
-        <v>41.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q27" t="n">
-        <v>68.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>89.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L28" t="n">
-        <v>79.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M28" t="n">
-        <v>79.54229711203628</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N28" t="n">
-        <v>55.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O28" t="n">
-        <v>71.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P28" t="n">
-        <v>95.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>91.99244221512848</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K29" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L29" t="n">
-        <v>85.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M29" t="n">
-        <v>60.50171533477999</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N29" t="n">
-        <v>57.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O29" t="n">
-        <v>68.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P29" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q29" t="n">
-        <v>108.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>88.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K30" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L30" t="n">
-        <v>31.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M30" t="n">
-        <v>14.61488351249858</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P30" t="n">
-        <v>26.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q30" t="n">
-        <v>68.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L31" t="n">
-        <v>79.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M31" t="n">
-        <v>80.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N31" t="n">
-        <v>55.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O31" t="n">
-        <v>86.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P31" t="n">
-        <v>95.19827131193951</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>91.99244221512848</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K32" t="n">
-        <v>101.6217957685986</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L32" t="n">
-        <v>84.58142974081102</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M32" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N32" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O32" t="n">
-        <v>68.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P32" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q32" t="n">
-        <v>123.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K33" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L33" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M33" t="n">
-        <v>14.28297331595775</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3319101965408322</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P33" t="n">
-        <v>41.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q33" t="n">
-        <v>83.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L34" t="n">
-        <v>79.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M34" t="n">
-        <v>65.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N34" t="n">
-        <v>70.0563199247463</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O34" t="n">
-        <v>86.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P34" t="n">
-        <v>95.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>106.9924422151285</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K35" t="n">
-        <v>101.6217957685986</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L35" t="n">
-        <v>85.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M35" t="n">
-        <v>60.50171533477997</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N35" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O35" t="n">
-        <v>53.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P35" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q35" t="n">
-        <v>108.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K36" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L36" t="n">
-        <v>31.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P36" t="n">
-        <v>41.38723432305521</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q36" t="n">
-        <v>83.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L37" t="n">
-        <v>64.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M37" t="n">
-        <v>79.54229711203627</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N37" t="n">
-        <v>70.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O37" t="n">
-        <v>86.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P37" t="n">
-        <v>95.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>91.99244221512848</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K38" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L38" t="n">
-        <v>85.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M38" t="n">
-        <v>61.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N38" t="n">
-        <v>57.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O38" t="n">
-        <v>53.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P38" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q38" t="n">
-        <v>123.3928403236653</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K39" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L39" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M39" t="n">
-        <v>14.61488351249857</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>24.02580104821803</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P39" t="n">
-        <v>26.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q39" t="n">
-        <v>83.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L40" t="n">
-        <v>64.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M40" t="n">
-        <v>79.54229711203627</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N40" t="n">
-        <v>70.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O40" t="n">
-        <v>86.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P40" t="n">
-        <v>95.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>106.9924422151285</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K41" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L41" t="n">
-        <v>70.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M41" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N41" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O41" t="n">
-        <v>67.70596488597788</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P41" t="n">
-        <v>95.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q41" t="n">
-        <v>123.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K42" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L42" t="n">
-        <v>31.38584257790156</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M42" t="n">
-        <v>14.88903392201834</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P42" t="n">
-        <v>41.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q42" t="n">
-        <v>68.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L43" t="n">
-        <v>79.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M43" t="n">
-        <v>80.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N43" t="n">
-        <v>70.05631992474632</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O43" t="n">
-        <v>86.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P43" t="n">
-        <v>80.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>91.99244221512848</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K44" t="n">
-        <v>86.62179576859864</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L44" t="n">
-        <v>70.18749034687164</v>
+        <v>86.82148686318189</v>
       </c>
       <c r="M44" t="n">
-        <v>46.10777594084058</v>
+        <v>64.61630209323866</v>
       </c>
       <c r="N44" t="n">
-        <v>42.1934354558874</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O44" t="n">
-        <v>53.31202549203849</v>
+        <v>71.07189926570237</v>
       </c>
       <c r="P44" t="n">
-        <v>80.3500761572796</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q44" t="n">
-        <v>108.9989009297259</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>73.79799459119499</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K45" t="n">
-        <v>47.18825972907597</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L45" t="n">
-        <v>16.65999298742133</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>9.025801048218028</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P45" t="n">
-        <v>26.77235081055665</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q45" t="n">
-        <v>68.3200382369649</v>
+        <v>75.5191492782957</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>74.3316188262731</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L46" t="n">
-        <v>64.91100415009073</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M46" t="n">
-        <v>65.14835771809688</v>
+        <v>72.56001021962936</v>
       </c>
       <c r="N46" t="n">
-        <v>55.66238053080693</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O46" t="n">
-        <v>71.93148927151491</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P46" t="n">
-        <v>80.8043319180001</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>415.286657113125</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>339.3101186986817</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>209.8559498719135</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>10.58448533451202</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,19 +23023,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.254196701981991</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>148.8590073883859</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>208.6536374254413</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0254576043324</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3443664756757</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,16 +23072,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3349133896257</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>112.1523498968738</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>89.10040643632074</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>99.62364547339784</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>171.5233597830831</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1300494495386</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>225.940816043239</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9837662437047</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>162.1630413598986</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>155.2335568944714</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>92.84921290355803</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>21.43145903899761</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,22 +23178,22 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.849047292483561</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>85.55804325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>176.969063508317</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
-        <v>223.8908931189395</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
-        <v>227.9147697561503</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
-        <v>286.3186359138679</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H11" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I11" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S11" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T11" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U11" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H12" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I12" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>65.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S12" t="n">
-        <v>161.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T12" t="n">
-        <v>197.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H13" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I13" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J13" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R13" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S13" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T13" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H14" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I14" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S14" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T14" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U14" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H15" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I15" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>65.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S15" t="n">
-        <v>161.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T15" t="n">
-        <v>197.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H16" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I16" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J16" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R16" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S16" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T16" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H17" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I17" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S17" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T17" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U17" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H18" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I18" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>65.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S18" t="n">
-        <v>161.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T18" t="n">
-        <v>197.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H19" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I19" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J19" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R19" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S19" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T19" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H20" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I20" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,25 +23974,25 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S20" t="n">
-        <v>171.898371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T20" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U20" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V20" t="n">
-        <v>312.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>334.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
-        <v>354.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
         <v>386.2379386560536</v>
@@ -24008,10 +24008,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>159.4964989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>132.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H21" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I21" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,22 +24053,22 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>65.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S21" t="n">
-        <v>146.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T21" t="n">
-        <v>197.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>236.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
@@ -24084,10 +24084,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>164.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>152.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H22" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I22" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J22" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R22" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S22" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T22" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24150,10 +24150,10 @@
         <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
-        <v>212.4976553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
-        <v>203.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="23">
@@ -24166,7 +24166,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>352.0608917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
         <v>354.683041620683</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H23" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I23" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S23" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T23" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U23" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>334.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>354.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>371.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H24" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I24" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,22 +24290,22 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>65.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S24" t="n">
-        <v>148.0434824245926</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T24" t="n">
-        <v>182.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U24" t="n">
-        <v>210.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>236.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>164.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C25" t="n">
         <v>167.2468210986278</v>
@@ -24333,19 +24333,19 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F25" t="n">
-        <v>132.2090480229313</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H25" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I25" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J25" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R25" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S25" t="n">
-        <v>200.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T25" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U25" t="n">
-        <v>271.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24406,22 +24406,22 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>339.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>391.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>399.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H26" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I26" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S26" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T26" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U26" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24466,7 +24466,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>356.519100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
         <v>386.2379386560536</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>123.5701209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H27" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I27" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,22 +24527,22 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>50.3020228318884</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S27" t="n">
-        <v>161.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T27" t="n">
-        <v>182.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>236.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
@@ -24564,7 +24564,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D28" t="n">
-        <v>135.4034730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E28" t="n">
         <v>146.4339626465692</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H28" t="n">
-        <v>143.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I28" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J28" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,22 +24603,22 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R28" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S28" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T28" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U28" t="n">
-        <v>271.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V28" t="n">
-        <v>237.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
         <v>286.522998336591</v>
@@ -24646,19 +24646,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>366.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>393.6640457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>399.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H29" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I29" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>68.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S29" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T29" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U29" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>121.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H30" t="n">
-        <v>91.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I30" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,22 +24764,22 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>52.0900228318884</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S30" t="n">
-        <v>161.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T30" t="n">
-        <v>197.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>236.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>152.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H31" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I31" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J31" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,31 +24840,31 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R31" t="n">
-        <v>141.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S31" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T31" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W31" t="n">
-        <v>273.310998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X31" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>203.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="32">
@@ -24877,10 +24877,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>350.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>339.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
         <v>381.9303700722618</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>401.0414912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H32" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I32" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,22 +24922,22 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S32" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T32" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U32" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>334.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
         <v>369.731100678469</v>
@@ -24962,19 +24962,19 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>142.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>130.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H33" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I33" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>52.0900228318884</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S33" t="n">
-        <v>161.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T33" t="n">
-        <v>182.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25041,22 +25041,22 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E34" t="n">
-        <v>133.2219626465692</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
-        <v>130.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>152.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H34" t="n">
-        <v>143.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I34" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J34" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R34" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S34" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T34" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>401.0414912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H35" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I35" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,19 +25159,19 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>68.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S35" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T35" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U35" t="n">
-        <v>236.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V35" t="n">
-        <v>312.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
@@ -25196,7 +25196,7 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>132.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
         <v>157.6450804554009</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>123.5701209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H36" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I36" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>50.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S36" t="n">
-        <v>161.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T36" t="n">
-        <v>197.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U36" t="n">
-        <v>210.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>152.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H37" t="n">
-        <v>143.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I37" t="n">
-        <v>128.084573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J37" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R37" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S37" t="n">
-        <v>200.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T37" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25360,16 +25360,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>391.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>399.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H38" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I38" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S38" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T38" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U38" t="n">
-        <v>238.049713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>371.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H39" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I39" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>50.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S39" t="n">
-        <v>146.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T39" t="n">
-        <v>182.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U39" t="n">
-        <v>212.6924481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25512,25 +25512,25 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D40" t="n">
-        <v>135.4034730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E40" t="n">
-        <v>131.4339626465692</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F40" t="n">
-        <v>130.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>152.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H40" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I40" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J40" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R40" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S40" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T40" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25588,7 +25588,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>350.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25597,16 +25597,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>393.6640457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H41" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I41" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,22 +25633,22 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S41" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T41" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U41" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V41" t="n">
-        <v>312.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>334.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H42" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I42" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,22 +25712,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>65.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S42" t="n">
-        <v>146.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T42" t="n">
-        <v>182.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U42" t="n">
-        <v>212.6924481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>236.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H43" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I43" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J43" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,22 +25788,22 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R43" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S43" t="n">
-        <v>202.6023521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T43" t="n">
-        <v>210.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U43" t="n">
-        <v>271.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V43" t="n">
-        <v>237.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
         <v>286.522998336591</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.2534912839793</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H44" t="n">
-        <v>328.729209150943</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I44" t="n">
-        <v>170.0248242437727</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>83.95940437331048</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S44" t="n">
-        <v>185.110371093783</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T44" t="n">
-        <v>218.5027741872469</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U44" t="n">
-        <v>251.261713209344</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.7821209367955</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H45" t="n">
-        <v>106.8135385761191</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I45" t="n">
-        <v>70.06785926650942</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>65.30202283188839</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S45" t="n">
-        <v>161.2554824245925</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T45" t="n">
-        <v>197.9019079401046</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9044481187107</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H46" t="n">
-        <v>158.0426151303904</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I46" t="n">
-        <v>141.296573287914</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J46" t="n">
-        <v>60.08381946093508</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>46.75104325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R46" t="n">
-        <v>156.1309979345465</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S46" t="n">
-        <v>215.8143521353329</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T46" t="n">
-        <v>225.9346058217241</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>339090.6085810206</v>
+        <v>338648.3274240561</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>338535.8515104846</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>338535.8515104846</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338535.8515104846</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>351830.8871469132</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>351830.8871469133</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>351830.8871469132</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>351830.8871469132</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>351830.8871469132</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>351830.8871469132</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>351830.8871469132</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>351830.8871469132</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>338535.8515104846</v>
+        <v>338810.6490978886</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>80630.55414858479</v>
+      </c>
+      <c r="C2" t="n">
         <v>80630.55414858478</v>
       </c>
-      <c r="C2" t="n">
-        <v>80630.55414858479</v>
-      </c>
       <c r="D2" t="n">
-        <v>80852.23746542638</v>
+        <v>80630.55414858478</v>
       </c>
       <c r="E2" t="n">
-        <v>88167.61728693679</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="F2" t="n">
-        <v>88167.6172869368</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="G2" t="n">
-        <v>88167.61728693679</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="H2" t="n">
-        <v>91354.72428693682</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="I2" t="n">
-        <v>91354.72428693682</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="J2" t="n">
-        <v>91354.72428693682</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="K2" t="n">
-        <v>91354.72428693683</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="L2" t="n">
-        <v>91354.72428693683</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="M2" t="n">
-        <v>91354.72428693679</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="N2" t="n">
-        <v>91354.72428693681</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="O2" t="n">
-        <v>91354.72428693681</v>
+        <v>87500.02638886588</v>
       </c>
       <c r="P2" t="n">
-        <v>88167.61728693683</v>
+        <v>87500.02638886588</v>
       </c>
     </row>
     <row r="3">
@@ -26319,10 +26319,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3425.656</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>206474.571</v>
+        <v>188622.9869705381</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26331,7 +26331,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4047.135</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="C4" t="n">
-        <v>43002.96221257856</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="D4" t="n">
-        <v>42632.40454112359</v>
+        <v>41731.10116290394</v>
       </c>
       <c r="E4" t="n">
-        <v>15254.58812504964</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="F4" t="n">
-        <v>15254.58812504964</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="G4" t="n">
-        <v>15254.58812504964</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="H4" t="n">
-        <v>16876.57203420532</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="I4" t="n">
-        <v>16876.57203420532</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="J4" t="n">
-        <v>16876.57203420532</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="K4" t="n">
-        <v>16876.57203420532</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="L4" t="n">
-        <v>16876.57203420532</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="M4" t="n">
-        <v>16876.57203420532</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="N4" t="n">
-        <v>16876.57203420532</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="O4" t="n">
-        <v>16876.57203420532</v>
+        <v>17445.5225022092</v>
       </c>
       <c r="P4" t="n">
-        <v>15254.58812504964</v>
+        <v>17445.5225022092</v>
       </c>
     </row>
     <row r="5">
@@ -26423,43 +26423,43 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>33714.8</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>5689.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="F5" t="n">
-        <v>5689.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="G5" t="n">
-        <v>5689.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="H5" t="n">
-        <v>6601.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="I5" t="n">
-        <v>6601.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="J5" t="n">
-        <v>6601.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="K5" t="n">
-        <v>6601.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="L5" t="n">
-        <v>6601.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="M5" t="n">
-        <v>6601.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="N5" t="n">
-        <v>6601.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="O5" t="n">
-        <v>6601.8</v>
+        <v>5118.204831146673</v>
       </c>
       <c r="P5" t="n">
-        <v>5689.8</v>
+        <v>5118.204831146673</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3999.991936006219</v>
+        <v>5271.852985680853</v>
       </c>
       <c r="C6" t="n">
-        <v>3999.991936006234</v>
+        <v>5271.852985680838</v>
       </c>
       <c r="D6" t="n">
-        <v>1079.3769243028</v>
+        <v>5271.852985680838</v>
       </c>
       <c r="E6" t="n">
-        <v>-139251.3418381128</v>
+        <v>-123686.6879150281</v>
       </c>
       <c r="F6" t="n">
-        <v>67223.22916188715</v>
+        <v>64936.29905551</v>
       </c>
       <c r="G6" t="n">
-        <v>67223.22916188714</v>
+        <v>64936.29905551</v>
       </c>
       <c r="H6" t="n">
-        <v>63829.2172527315</v>
+        <v>64936.29905551</v>
       </c>
       <c r="I6" t="n">
-        <v>67876.35225273149</v>
+        <v>64936.29905551</v>
       </c>
       <c r="J6" t="n">
-        <v>67876.35225273149</v>
+        <v>64936.29905551</v>
       </c>
       <c r="K6" t="n">
-        <v>67876.35225273151</v>
+        <v>64936.29905551</v>
       </c>
       <c r="L6" t="n">
-        <v>67876.35225273151</v>
+        <v>64936.29905551</v>
       </c>
       <c r="M6" t="n">
-        <v>67876.35225273146</v>
+        <v>64936.29905551</v>
       </c>
       <c r="N6" t="n">
-        <v>67876.35225273148</v>
+        <v>64936.29905551</v>
       </c>
       <c r="O6" t="n">
-        <v>67876.35225273148</v>
+        <v>64936.29905551</v>
       </c>
       <c r="P6" t="n">
-        <v>67223.22916188718</v>
+        <v>64936.29905551</v>
       </c>
     </row>
   </sheetData>
@@ -26681,43 +26681,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="F3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="G3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="H3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="I3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="J3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="K3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="L3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="M3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="N3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="O3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="P3" t="n">
-        <v>261</v>
+        <v>234.7800381259942</v>
       </c>
     </row>
     <row r="4">
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26898,10 +26898,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>257</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01608040201005024</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1646834170854271</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6199396984924624</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.364804020100503</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.04548743718593</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.537608040201005</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.823577889447236</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.869266331658292</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.709366834170854</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.312381909547739</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.736502512562814</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.010110552763819</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3664321608040202</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.07039195979899496</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001286432160804019</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008603773584905661</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08309433962264152</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2962264150943397</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.812867924528302</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.389320754716981</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.86811320754717</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.237698113207547</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.047056603773585</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.642943396226415</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.098264150943396</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5341886792452832</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1598113207547169</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03467924528301886</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0005660377358490568</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00721311475409836</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06413114754098365</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2169180327868853</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.509967213114754</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8380327868852456</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.072393442622951</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.130688524590164</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.103803278688525</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.019540983606558</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8723934426229504</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3243278688524589</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1257049180327868</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.03081967213114753</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0003934426229508201</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I11" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J11" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K11" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L11" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M11" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N11" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O11" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P11" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R11" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S11" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T11" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H12" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I12" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J12" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K12" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L12" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M12" t="n">
-        <v>142.1340339220183</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P12" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q12" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R12" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S12" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T12" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H13" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I13" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J13" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K13" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L13" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M13" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N13" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O13" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P13" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q13" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R13" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S13" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T13" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I14" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J14" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K14" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L14" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M14" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N14" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O14" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P14" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R14" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S14" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T14" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H15" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I15" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J15" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K15" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L15" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M15" t="n">
-        <v>142.1340339220183</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P15" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q15" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R15" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S15" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T15" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H16" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I16" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J16" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K16" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L16" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M16" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N16" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O16" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P16" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q16" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R16" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S16" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T16" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U16" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H17" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I17" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J17" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K17" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L17" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M17" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N17" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O17" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P17" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R17" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S17" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T17" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H18" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I18" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J18" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K18" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L18" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N18" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P18" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q18" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R18" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S18" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T18" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H19" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I19" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J19" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K19" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L19" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M19" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N19" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O19" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P19" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q19" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R19" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S19" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T19" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H20" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I20" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J20" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K20" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L20" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M20" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N20" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O20" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P20" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R20" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S20" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T20" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H21" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I21" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J21" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K21" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L21" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M21" t="n">
-        <v>142.245</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N21" t="n">
-        <v>146.0098018867925</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P21" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q21" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R21" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S21" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T21" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H22" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I22" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J22" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K22" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L22" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M22" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N22" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O22" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P22" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q22" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R22" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S22" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T22" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U22" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H23" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I23" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J23" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K23" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L23" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M23" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N23" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O23" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P23" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R23" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S23" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T23" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H24" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I24" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J24" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K24" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L24" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M24" t="n">
-        <v>142.245</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N24" t="n">
-        <v>146.0098018867925</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P24" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q24" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R24" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S24" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T24" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H25" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I25" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J25" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K25" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L25" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M25" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N25" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O25" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P25" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q25" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R25" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S25" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T25" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H26" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I26" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J26" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K26" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L26" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M26" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N26" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O26" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P26" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R26" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S26" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T26" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H27" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I27" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J27" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K27" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L27" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M27" t="n">
-        <v>142.245</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N27" t="n">
-        <v>146.0098018867925</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P27" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q27" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R27" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S27" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T27" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H28" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I28" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J28" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K28" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L28" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M28" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N28" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O28" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P28" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q28" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R28" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S28" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T28" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U28" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H29" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I29" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J29" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K29" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L29" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M29" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N29" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O29" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P29" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R29" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S29" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T29" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U29" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H30" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I30" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J30" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K30" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L30" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M30" t="n">
-        <v>142.245</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N30" t="n">
-        <v>146.0098018867925</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P30" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q30" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R30" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S30" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T30" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H31" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I31" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J31" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K31" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L31" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M31" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N31" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O31" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P31" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q31" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R31" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S31" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T31" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U31" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H32" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I32" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J32" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K32" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L32" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M32" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N32" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O32" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P32" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R32" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S32" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T32" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H33" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I33" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J33" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K33" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L33" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M33" t="n">
-        <v>142.245</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N33" t="n">
-        <v>146.0098018867925</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P33" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q33" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R33" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S33" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T33" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U33" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H34" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I34" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J34" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K34" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L34" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M34" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N34" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O34" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P34" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q34" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R34" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S34" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T34" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U34" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H35" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I35" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J35" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K35" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L35" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M35" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N35" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O35" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P35" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R35" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S35" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T35" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H36" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I36" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J36" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K36" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L36" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M36" t="n">
-        <v>142.245</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N36" t="n">
-        <v>146.0098018867925</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P36" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q36" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R36" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S36" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T36" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U36" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H37" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I37" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J37" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K37" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L37" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M37" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N37" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O37" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P37" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q37" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R37" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S37" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T37" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H38" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I38" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J38" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K38" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L38" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M38" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N38" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O38" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P38" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R38" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S38" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T38" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H39" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I39" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J39" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K39" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L39" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M39" t="n">
-        <v>142.245</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N39" t="n">
-        <v>146.0098018867925</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P39" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R39" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S39" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T39" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H40" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I40" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J40" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K40" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L40" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M40" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N40" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O40" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P40" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q40" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R40" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S40" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T40" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H41" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I41" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J41" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K41" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L41" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M41" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N41" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O41" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P41" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R41" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S41" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T41" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U41" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H42" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I42" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J42" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K42" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L42" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M42" t="n">
-        <v>142.245</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N42" t="n">
-        <v>146.0098018867925</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P42" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q42" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R42" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S42" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T42" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H43" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I43" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J43" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K43" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L43" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M43" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N43" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O43" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P43" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q43" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R43" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S43" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T43" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.049246231155778</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H44" t="n">
-        <v>10.74559296482412</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I44" t="n">
-        <v>40.45106532663318</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J44" t="n">
-        <v>89.05346231155781</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K44" t="n">
-        <v>133.4680552763819</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L44" t="n">
-        <v>165.5789246231156</v>
+        <v>148.9449281068053</v>
       </c>
       <c r="M44" t="n">
-        <v>184.2384572864322</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N44" t="n">
-        <v>187.2196281407035</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O44" t="n">
-        <v>176.7861859296482</v>
+        <v>159.0263121559844</v>
       </c>
       <c r="P44" t="n">
-        <v>150.8829195979899</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3067889447236</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R44" t="n">
-        <v>65.9097135678392</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S44" t="n">
-        <v>23.90969849246232</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T44" t="n">
-        <v>4.593075376884421</v>
+        <v>4.131656751342872</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H45" t="n">
-        <v>5.42190566037736</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I45" t="n">
-        <v>19.32877358490566</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J45" t="n">
-        <v>53.03963207547171</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K45" t="n">
-        <v>90.65317924528303</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L45" t="n">
-        <v>121.8943867924528</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M45" t="n">
-        <v>142.1340339220183</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N45" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>133.5704433962264</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P45" t="n">
-        <v>107.2020566037736</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q45" t="n">
-        <v>71.66173584905661</v>
+        <v>64.46262480772582</v>
       </c>
       <c r="R45" t="n">
-        <v>34.85581132075473</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S45" t="n">
-        <v>10.42768867924528</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T45" t="n">
-        <v>2.262820754716981</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U45" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4233738392435961</v>
       </c>
       <c r="H46" t="n">
-        <v>4.184557377049183</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I46" t="n">
-        <v>14.15390163934427</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J46" t="n">
-        <v>33.2753606557377</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K46" t="n">
-        <v>54.68163934426228</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L46" t="n">
-        <v>69.97367213114755</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M46" t="n">
-        <v>73.77742622950818</v>
+        <v>66.36577372797569</v>
       </c>
       <c r="N46" t="n">
-        <v>72.02316393442626</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O46" t="n">
-        <v>66.52504918032788</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P46" t="n">
-        <v>56.92367213114751</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q46" t="n">
-        <v>39.411</v>
+        <v>35.45178575702512</v>
       </c>
       <c r="R46" t="n">
-        <v>21.16239344262294</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S46" t="n">
-        <v>8.202245901639341</v>
+        <v>7.378251362090666</v>
       </c>
       <c r="T46" t="n">
-        <v>2.010983606557376</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U46" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -36033,7 +36033,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -36045,16 +36045,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36115,22 +36115,22 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>14.72584959048022</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>14.66808980345917</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36194,19 +36194,19 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -36276,7 +36276,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -36285,13 +36285,13 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36349,7 +36349,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -36358,19 +36358,19 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1109660779816579</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>14.28297331595774</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36437,16 +36437,16 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -36507,13 +36507,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -36522,7 +36522,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -36595,16 +36595,16 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>14.72584959048022</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>14.66808980345917</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36668,13 +36668,13 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -36683,7 +36683,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -36750,16 +36750,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -36823,19 +36823,19 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>14.72584959048022</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>14.66808980345917</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -36908,19 +36908,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -36984,10 +36984,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -36996,13 +36996,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37069,19 +37069,19 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37145,19 +37145,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -37218,16 +37218,16 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1109660779816579</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>14.66808980345917</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>14.61488351249857</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37385,16 +37385,16 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -37461,13 +37461,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -37476,7 +37476,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37543,19 +37543,19 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>14.72584959048022</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>14.66808980345917</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37622,16 +37622,16 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -37692,7 +37692,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -37707,13 +37707,13 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37777,19 +37777,19 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>14.72584959048023</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>14.66808980345917</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37856,16 +37856,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>14.39393939393939</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
